--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260615.xlsx
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>197,792,281</t>
+          <t>1,686,579</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,686,579</t>
+          <t>197,792,281</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
